--- a/08_third-party-ai-model-risk-assessment/exercises/starter/vendor_governance_starter.xlsx
+++ b/08_third-party-ai-model-risk-assessment/exercises/starter/vendor_governance_starter.xlsx
@@ -966,25 +966,29 @@
           <t>Limited</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>40</v>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>[Your response here — name the security certification(s) this vendor publishes (e.g., SOC2, ISO27001, FedRAMP, or "None published"). Compare to the certs listed for the pre-filled vendors in rows 2-4. If the vendor cannot produce certifications on request, treat that as a documented red flag rather than leaving it blank.]</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>[Your response here — rate Low / Medium / High based on whether this vendor publishes model cards, training-data documentation, and eval results. The Scenario Brief signals weak governance for this vendor — align your rating with that evidence and with how the pre-filled vendors are rated in column E.]</t>
+        </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the geography (e.g., US-only, EU-only, multi-region, specific cloud provider data centers). This drives GDPR and data-residency exposure for InsureLogic's EU policyholders — flag if the vendor cannot guarantee region pinning.]</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — answer Yes / No / Partial / Unknown depending on whether the vendor publishes bias and fairness evaluations. For an automated claims-processing model, missing bias testing is both a NAIC regulatory issue and a reputational risk.]</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the uptime percentage this vendor commits to in their published SLA (e.g., 99.9%, 99.95%, 99.99%). If the SLA does not specify a numeric commitment, write "Not specified" — that itself is a finding.]</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -1029,27 +1033,27 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the security certification(s) this vendor publishes. The Scenario Brief positions SafeGuard AI as a strong-governance vendor, so your answer should reflect industry-standard certs you would expect from such a vendor. Use the same format as rows 2-4.]</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — rate Low / Medium / High based on the vendor's published model documentation, training-data disclosures, and eval transparency. Match the rating to the vendor's overall governance posture relative to the pre-filled vendors.]</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the processing geography. Think about what residency options a vendor pitched as enterprise-grade would typically offer to a US-and-EU insurance buyer.]</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Yes / No / Partial / Unknown. A vendor positioning itself on strong governance should be publishing bias evals; your answer should reflect that expectation and be consistent with the Bias Testing answers in rows 2-4.]</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the uptime percentage this vendor commits to. Compare against the SLA uptimes in rows 2-4 to pick a value consistent with the vendor's tier and the I6 response-time SLA already filled in.]</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -1232,134 +1236,150 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="11" t="n"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Throughput</t>
+        </is>
+      </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the minimum acceptable threshold (worst-case still tolerated) for the metric in column A. Use the same units as the metric (%, ms, req/sec, hours) and mirror the format style of rows 2-3.]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the target threshold (what you actually expect the vendor to hit). Should be measurably better than your Min Threshold in column B, in the same units.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how this metric is measured (e.g., automated tooling, log analysis, ticket timestamps, transaction logs). Match the specificity of the pre-filled rows.]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how often this metric is monitored (e.g., continuous, real-time, hourly, daily, per-incident). Frequency should match the metric's criticality.]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the financial or contractual consequence when the vendor misses the target (e.g., service credit %, penalty multiplier, root-cause SLA). Should be enforceable and tied to the breach severity.]</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the escalation tier or path triggered when this SLA is breached. Use the Tier 1 / Tier 2 / Tier 3 convention shown in rows 2-3 and align tier with business criticality of the metric.]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="11" t="n"/>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Error Rate</t>
+        </is>
+      </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the minimum acceptable threshold (worst-case still tolerated) for the metric in column A. Use the same units as the metric (%, ms, req/sec, hours) and mirror the format style of rows 2-3.]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the target threshold (what you actually expect the vendor to hit). Should be measurably better than your Min Threshold in column B, in the same units.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how this metric is measured (e.g., automated tooling, log analysis, ticket timestamps, transaction logs). Match the specificity of the pre-filled rows.]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how often this metric is monitored (e.g., continuous, real-time, hourly, daily, per-incident). Frequency should match the metric's criticality.]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the financial or contractual consequence when the vendor misses the target (e.g., service credit %, penalty multiplier, root-cause SLA). Should be enforceable and tied to the breach severity.]</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the escalation tier or path triggered when this SLA is breached. Use the Tier 1 / Tier 2 / Tier 3 convention shown in rows 2-3 and align tier with business criticality of the metric.]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Data Processing Time</t>
+        </is>
+      </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the minimum acceptable threshold (worst-case still tolerated) for the metric in column A. Use the same units as the metric (%, ms, req/sec, hours) and mirror the format style of rows 2-3.]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the target threshold (what you actually expect the vendor to hit). Should be measurably better than your Min Threshold in column B, in the same units.]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how this metric is measured (e.g., automated tooling, log analysis, ticket timestamps, transaction logs). Match the specificity of the pre-filled rows.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how often this metric is monitored (e.g., continuous, real-time, hourly, daily, per-incident). Frequency should match the metric's criticality.]</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the financial or contractual consequence when the vendor misses the target (e.g., service credit %, penalty multiplier, root-cause SLA). Should be enforceable and tied to the breach severity.]</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the escalation tier or path triggered when this SLA is breached. Use the Tier 1 / Tier 2 / Tier 3 convention shown in rows 2-3 and align tier with business criticality of the metric.]</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Support Response Time</t>
+        </is>
+      </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the minimum acceptable threshold (worst-case still tolerated) for the metric in column A. Use the same units as the metric (%, ms, req/sec, hours) and mirror the format style of rows 2-3.]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the target threshold (what you actually expect the vendor to hit). Should be measurably better than your Min Threshold in column B, in the same units.]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how this metric is measured (e.g., automated tooling, log analysis, ticket timestamps, transaction logs). Match the specificity of the pre-filled rows.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — how often this metric is monitored (e.g., continuous, real-time, hourly, daily, per-incident). Frequency should match the metric's criticality.]</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the financial or contractual consequence when the vendor misses the target (e.g., service credit %, penalty multiplier, root-cause SLA). Should be enforceable and tied to the breach severity.]</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the escalation tier or path triggered when this SLA is breached. Use the Tier 1 / Tier 2 / Tier 3 convention shown in rows 2-3 and align tier with business criticality of the metric.]</t>
         </is>
       </c>
     </row>
@@ -1678,154 +1698,170 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="11" t="n"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SLA Violation (&gt;1 week)</t>
+        </is>
+      </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High probability of this scenario occurring within the contract term. Calibrate against the pre-filled rows (e.g., breach = Medium, shutdown = Low).]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High / Critical impact on InsureLogic's claims-processing operations if this scenario materializes. Should be consistent with how the pre-filled scenarios are rated.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the primary mitigation or response action (e.g., contract clause, redundant vendor, remediation mandate, version management). Match the action-oriented style in rows 2-3.]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which of the 5 vendors (NovaMind, CloudVault, TitanScale, DeepLens, SafeGuard) you would fail over to for this scenario, or note "Multi-vendor approach" if no single backup applies. Pick a vendor whose risk profile actually fits the scenario.]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — realistic migration timeline (e.g., hours, days, weeks). Should be tighter for high-impact scenarios and align with the migration timelines in rows 2-3.]</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — what data must be portable out (e.g., API export, encrypted dump, audit trail, fine-tuning dataset). Tailor to what would actually be needed to recover from this specific scenario.]</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — who gets notified, when, and through what channel. Reference the regulatory and stakeholder context from the Scenario Brief (NAIC, executives, legal/compliance, customers).]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="11" t="n"/>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Price Increase (&gt;20%)</t>
+        </is>
+      </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High probability of this scenario occurring within the contract term. Calibrate against the pre-filled rows (e.g., breach = Medium, shutdown = Low).]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High / Critical impact on InsureLogic's claims-processing operations if this scenario materializes. Should be consistent with how the pre-filled scenarios are rated.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the primary mitigation or response action (e.g., contract clause, redundant vendor, remediation mandate, version management). Match the action-oriented style in rows 2-3.]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which of the 5 vendors (NovaMind, CloudVault, TitanScale, DeepLens, SafeGuard) you would fail over to for this scenario, or note "Multi-vendor approach" if no single backup applies. Pick a vendor whose risk profile actually fits the scenario.]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — realistic migration timeline (e.g., hours, days, weeks). Should be tighter for high-impact scenarios and align with the migration timelines in rows 2-3.]</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — what data must be portable out (e.g., API export, encrypted dump, audit trail, fine-tuning dataset). Tailor to what would actually be needed to recover from this specific scenario.]</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — who gets notified, when, and through what channel. Reference the regulatory and stakeholder context from the Scenario Brief (NAIC, executives, legal/compliance, customers).]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>API Deprecation</t>
+        </is>
+      </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High probability of this scenario occurring within the contract term. Calibrate against the pre-filled rows (e.g., breach = Medium, shutdown = Low).]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High / Critical impact on InsureLogic's claims-processing operations if this scenario materializes. Should be consistent with how the pre-filled scenarios are rated.]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the primary mitigation or response action (e.g., contract clause, redundant vendor, remediation mandate, version management). Match the action-oriented style in rows 2-3.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which of the 5 vendors (NovaMind, CloudVault, TitanScale, DeepLens, SafeGuard) you would fail over to for this scenario, or note "Multi-vendor approach" if no single backup applies. Pick a vendor whose risk profile actually fits the scenario.]</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — realistic migration timeline (e.g., hours, days, weeks). Should be tighter for high-impact scenarios and align with the migration timelines in rows 2-3.]</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — what data must be portable out (e.g., API export, encrypted dump, audit trail, fine-tuning dataset). Tailor to what would actually be needed to recover from this specific scenario.]</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — who gets notified, when, and through what channel. Reference the regulatory and stakeholder context from the Scenario Brief (NAIC, executives, legal/compliance, customers).]</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Regulatory Non-Compliance</t>
+        </is>
+      </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High probability of this scenario occurring within the contract term. Calibrate against the pre-filled rows (e.g., breach = Medium, shutdown = Low).]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — Low / Medium / High / Critical impact on InsureLogic's claims-processing operations if this scenario materializes. Should be consistent with how the pre-filled scenarios are rated.]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — the primary mitigation or response action (e.g., contract clause, redundant vendor, remediation mandate, version management). Match the action-oriented style in rows 2-3.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which of the 5 vendors (NovaMind, CloudVault, TitanScale, DeepLens, SafeGuard) you would fail over to for this scenario, or note "Multi-vendor approach" if no single backup applies. Pick a vendor whose risk profile actually fits the scenario.]</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — realistic migration timeline (e.g., hours, days, weeks). Should be tighter for high-impact scenarios and align with the migration timelines in rows 2-3.]</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — what data must be portable out (e.g., API export, encrypted dump, audit trail, fine-tuning dataset). Tailor to what would actually be needed to recover from this specific scenario.]</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — who gets notified, when, and through what channel. Reference the regulatory and stakeholder context from the Scenario Brief (NAIC, executives, legal/compliance, customers).]</t>
         </is>
       </c>
     </row>

--- a/08_third-party-ai-model-risk-assessment/exercises/starter/vendor_governance_starter.xlsx
+++ b/08_third-party-ai-model-risk-assessment/exercises/starter/vendor_governance_starter.xlsx
@@ -648,7 +648,7 @@
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Weights: Security 30%, Data Handling 25%, Transparency 20%, Financial Stability 15%, SLA 10%</t>
+          <t>Weights (example allocation across the 7 dimensions): Security 25%, Data Handling 20%, Transparency 15%, Financial Stability 10%, SLA Compliance 10%, Exit Strategy 10%, AI Model Governance 10%</t>
         </is>
       </c>
       <c r="B15" s="13" t="n"/>
